--- a/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MAR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6AC55E9-CEFF-43F7-BD51-204EEAF6E65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{823480AE-9B63-4828-BDF8-4F3F308C9FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2576,7 +2576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B830467A-96FB-4B3D-8D32-B50AE6FC7D63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5137311-EED4-4AF1-B327-44AC229EA250}">
   <dimension ref="B2:AF348"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8935,7 +8935,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E8228A-ADA9-4AB5-BB13-C1F75CB61681}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16BA2B46-6736-4756-9BB5-B61BAA518529}">
   <dimension ref="B9:L17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19243,7 +19243,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC7642FA-6B38-41FE-A6A9-7033834D0A7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B07A636E-46F4-4D2B-B255-CD7667E5728B}">
   <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
